--- a/synthetic_dataset.xlsx
+++ b/synthetic_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\Диплом\Датасеты\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44BE00D-5C45-45B7-9E3E-D9D8B8B7EE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6596D0C9-40CF-4320-8DBD-A8E69718436D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Tasks" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tasks!$A$1:$C$1001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tasks!$A$1:$G$1001</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -314,7 +314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -331,6 +331,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -498,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -550,7 +551,7 @@
         <v>1.19</v>
       </c>
       <c r="D3" s="3">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="E3" s="3">
         <v>1.02</v>
@@ -629,13 +630,13 @@
         <v>11</v>
       </c>
       <c r="B8" s="3">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="C8" s="3">
         <v>0.92</v>
       </c>
       <c r="D8" s="3">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="E8" s="3">
         <v>0.83</v>
@@ -646,7 +647,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="3">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="C9" s="3">
         <v>1.1299999999999999</v>
@@ -666,7 +667,7 @@
         <v>1.08</v>
       </c>
       <c r="C10" s="3">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="D10" s="3">
         <v>0.95</v>
@@ -680,13 +681,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="C11" s="3">
         <v>1.1399999999999999</v>
       </c>
       <c r="D11" s="3">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="E11" s="3">
         <v>1.1100000000000001</v>
@@ -714,7 +715,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="3">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="C13" s="3">
         <v>0.84</v>
@@ -751,7 +752,7 @@
         <v>0.86</v>
       </c>
       <c r="C15" s="3">
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D15" s="3">
         <v>1.17</v>
@@ -776,6 +777,9 @@
       <c r="E16" s="3">
         <v>0.95</v>
       </c>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -925,11 +929,11 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E6" s="5">
         <f>VLOOKUP(B6,Assignee!$A$2:$E$16,Tasks!F6,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F6" s="6">
         <v>3</v>
@@ -949,11 +953,11 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E7" s="5">
         <f>VLOOKUP(B7,Assignee!$A$2:$E$16,Tasks!F7,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F7" s="6">
         <v>2</v>
@@ -1141,11 +1145,11 @@
         <v>25</v>
       </c>
       <c r="D15">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E15" s="5">
         <f>VLOOKUP(B15,Assignee!$A$2:$E$16,Tasks!F15,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F15" s="6">
         <v>2</v>
@@ -1213,11 +1217,11 @@
         <v>25</v>
       </c>
       <c r="D18">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E18" s="5">
         <f>VLOOKUP(B18,Assignee!$A$2:$E$16,Tasks!F18,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F18" s="6">
         <v>2</v>
@@ -1813,11 +1817,11 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E43" s="5">
         <f>VLOOKUP(B43,Assignee!$A$2:$E$16,Tasks!F43,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F43" s="6">
         <v>4</v>
@@ -1861,11 +1865,11 @@
         <v>25</v>
       </c>
       <c r="D45">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E45" s="5">
         <f>VLOOKUP(B45,Assignee!$A$2:$E$16,Tasks!F45,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F45" s="6">
         <v>2</v>
@@ -1885,11 +1889,11 @@
         <v>25</v>
       </c>
       <c r="D46">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E46" s="5">
         <f>VLOOKUP(B46,Assignee!$A$2:$E$16,Tasks!F46,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F46" s="6">
         <v>2</v>
@@ -1957,11 +1961,11 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E49" s="5">
         <f>VLOOKUP(B49,Assignee!$A$2:$E$16,Tasks!F49,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F49" s="6">
         <v>4</v>
@@ -2053,11 +2057,11 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E53" s="5">
         <f>VLOOKUP(B53,Assignee!$A$2:$E$16,Tasks!F53,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F53" s="6">
         <v>4</v>
@@ -2125,11 +2129,11 @@
         <v>31</v>
       </c>
       <c r="D56">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E56" s="5">
         <f>VLOOKUP(B56,Assignee!$A$2:$E$16,Tasks!F56,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F56" s="6">
         <v>3</v>
@@ -2245,11 +2249,11 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E61" s="5">
         <f>VLOOKUP(B61,Assignee!$A$2:$E$16,Tasks!F61,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F61" s="6">
         <v>4</v>
@@ -2269,11 +2273,11 @@
         <v>31</v>
       </c>
       <c r="D62">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E62" s="5">
         <f>VLOOKUP(B62,Assignee!$A$2:$E$16,Tasks!F62,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F62" s="6">
         <v>3</v>
@@ -2533,11 +2537,11 @@
         <v>25</v>
       </c>
       <c r="D73">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E73" s="5">
         <f>VLOOKUP(B73,Assignee!$A$2:$E$16,Tasks!F73,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F73" s="6">
         <v>2</v>
@@ -2677,11 +2681,11 @@
         <v>31</v>
       </c>
       <c r="D79">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E79" s="5">
         <f>VLOOKUP(B79,Assignee!$A$2:$E$16,Tasks!F79,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F79" s="6">
         <v>3</v>
@@ -2917,11 +2921,11 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E89" s="5">
         <f>VLOOKUP(B89,Assignee!$A$2:$E$16,Tasks!F89,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F89" s="6">
         <v>4</v>
@@ -2941,11 +2945,11 @@
         <v>31</v>
       </c>
       <c r="D90">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E90" s="5">
         <f>VLOOKUP(B90,Assignee!$A$2:$E$16,Tasks!F90,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F90" s="6">
         <v>3</v>
@@ -3349,11 +3353,11 @@
         <v>31</v>
       </c>
       <c r="D107">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E107" s="5">
         <f>VLOOKUP(B107,Assignee!$A$2:$E$16,Tasks!F107,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F107" s="6">
         <v>3</v>
@@ -3421,11 +3425,11 @@
         <v>25</v>
       </c>
       <c r="D110">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E110" s="5">
         <f>VLOOKUP(B110,Assignee!$A$2:$E$16,Tasks!F110,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F110" s="6">
         <v>2</v>
@@ -3445,11 +3449,11 @@
         <v>25</v>
       </c>
       <c r="D111">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E111" s="5">
         <f>VLOOKUP(B111,Assignee!$A$2:$E$16,Tasks!F111,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F111" s="6">
         <v>2</v>
@@ -3613,11 +3617,11 @@
         <v>31</v>
       </c>
       <c r="D118">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E118" s="5">
         <f>VLOOKUP(B118,Assignee!$A$2:$E$16,Tasks!F118,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F118" s="6">
         <v>3</v>
@@ -3709,11 +3713,11 @@
         <v>31</v>
       </c>
       <c r="D122">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E122" s="5">
         <f>VLOOKUP(B122,Assignee!$A$2:$E$16,Tasks!F122,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F122" s="6">
         <v>3</v>
@@ -3805,11 +3809,11 @@
         <v>25</v>
       </c>
       <c r="D126">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E126" s="5">
         <f>VLOOKUP(B126,Assignee!$A$2:$E$16,Tasks!F126,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F126" s="6">
         <v>2</v>
@@ -3973,11 +3977,11 @@
         <v>31</v>
       </c>
       <c r="D133">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E133" s="5">
         <f>VLOOKUP(B133,Assignee!$A$2:$E$16,Tasks!F133,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F133" s="6">
         <v>3</v>
@@ -3997,11 +4001,11 @@
         <v>25</v>
       </c>
       <c r="D134">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E134" s="5">
         <f>VLOOKUP(B134,Assignee!$A$2:$E$16,Tasks!F134,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F134" s="6">
         <v>2</v>
@@ -4189,11 +4193,11 @@
         <v>25</v>
       </c>
       <c r="D142">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E142" s="5">
         <f>VLOOKUP(B142,Assignee!$A$2:$E$16,Tasks!F142,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F142" s="6">
         <v>2</v>
@@ -4381,11 +4385,11 @@
         <v>25</v>
       </c>
       <c r="D150">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E150" s="5">
         <f>VLOOKUP(B150,Assignee!$A$2:$E$16,Tasks!F150,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F150" s="6">
         <v>2</v>
@@ -4501,11 +4505,11 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E155" s="5">
         <f>VLOOKUP(B155,Assignee!$A$2:$E$16,Tasks!F155,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F155" s="6">
         <v>4</v>
@@ -4717,11 +4721,11 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E164" s="5">
         <f>VLOOKUP(B164,Assignee!$A$2:$E$16,Tasks!F164,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F164" s="6">
         <v>4</v>
@@ -5341,11 +5345,11 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E190" s="5">
         <f>VLOOKUP(B190,Assignee!$A$2:$E$16,Tasks!F190,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F190" s="6">
         <v>4</v>
@@ -5389,11 +5393,11 @@
         <v>25</v>
       </c>
       <c r="D192">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E192" s="5">
         <f>VLOOKUP(B192,Assignee!$A$2:$E$16,Tasks!F192,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F192" s="6">
         <v>2</v>
@@ -5485,11 +5489,11 @@
         <v>25</v>
       </c>
       <c r="D196">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E196" s="5">
         <f>VLOOKUP(B196,Assignee!$A$2:$E$16,Tasks!F196,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F196" s="6">
         <v>2</v>
@@ -5581,11 +5585,11 @@
         <v>25</v>
       </c>
       <c r="D200">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E200" s="5">
         <f>VLOOKUP(B200,Assignee!$A$2:$E$16,Tasks!F200,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F200" s="6">
         <v>2</v>
@@ -6085,11 +6089,11 @@
         <v>25</v>
       </c>
       <c r="D221">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E221" s="5">
         <f>VLOOKUP(B221,Assignee!$A$2:$E$16,Tasks!F221,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F221" s="6">
         <v>2</v>
@@ -6133,11 +6137,11 @@
         <v>25</v>
       </c>
       <c r="D223">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E223" s="5">
         <f>VLOOKUP(B223,Assignee!$A$2:$E$16,Tasks!F223,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F223" s="6">
         <v>2</v>
@@ -6181,11 +6185,11 @@
         <v>25</v>
       </c>
       <c r="D225">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E225" s="5">
         <f>VLOOKUP(B225,Assignee!$A$2:$E$16,Tasks!F225,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F225" s="6">
         <v>2</v>
@@ -6325,11 +6329,11 @@
         <v>25</v>
       </c>
       <c r="D231">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E231" s="5">
         <f>VLOOKUP(B231,Assignee!$A$2:$E$16,Tasks!F231,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F231" s="6">
         <v>2</v>
@@ -6397,11 +6401,11 @@
         <v>31</v>
       </c>
       <c r="D234">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E234" s="5">
         <f>VLOOKUP(B234,Assignee!$A$2:$E$16,Tasks!F234,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F234" s="6">
         <v>3</v>
@@ -6445,11 +6449,11 @@
         <v>25</v>
       </c>
       <c r="D236">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E236" s="5">
         <f>VLOOKUP(B236,Assignee!$A$2:$E$16,Tasks!F236,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F236" s="6">
         <v>2</v>
@@ -6469,11 +6473,11 @@
         <v>25</v>
       </c>
       <c r="D237">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E237" s="5">
         <f>VLOOKUP(B237,Assignee!$A$2:$E$16,Tasks!F237,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F237" s="6">
         <v>2</v>
@@ -6661,11 +6665,11 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E245" s="5">
         <f>VLOOKUP(B245,Assignee!$A$2:$E$16,Tasks!F245,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F245" s="6">
         <v>4</v>
@@ -6709,11 +6713,11 @@
         <v>25</v>
       </c>
       <c r="D247">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E247" s="5">
         <f>VLOOKUP(B247,Assignee!$A$2:$E$16,Tasks!F247,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F247" s="6">
         <v>2</v>
@@ -6853,11 +6857,11 @@
         <v>31</v>
       </c>
       <c r="D253">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E253" s="5">
         <f>VLOOKUP(B253,Assignee!$A$2:$E$16,Tasks!F253,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F253" s="6">
         <v>3</v>
@@ -7309,11 +7313,11 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E272" s="5">
         <f>VLOOKUP(B272,Assignee!$A$2:$E$16,Tasks!F272,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F272" s="6">
         <v>4</v>
@@ -7501,11 +7505,11 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E280" s="5">
         <f>VLOOKUP(B280,Assignee!$A$2:$E$16,Tasks!F280,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F280" s="6">
         <v>4</v>
@@ -7525,11 +7529,11 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E281" s="5">
         <f>VLOOKUP(B281,Assignee!$A$2:$E$16,Tasks!F281,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F281" s="6">
         <v>4</v>
@@ -7597,11 +7601,11 @@
         <v>25</v>
       </c>
       <c r="D284">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E284" s="5">
         <f>VLOOKUP(B284,Assignee!$A$2:$E$16,Tasks!F284,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F284" s="6">
         <v>2</v>
@@ -7741,11 +7745,11 @@
         <v>31</v>
       </c>
       <c r="D290">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E290" s="5">
         <f>VLOOKUP(B290,Assignee!$A$2:$E$16,Tasks!F290,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F290" s="6">
         <v>3</v>
@@ -7861,11 +7865,11 @@
         <v>25</v>
       </c>
       <c r="D295">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E295" s="5">
         <f>VLOOKUP(B295,Assignee!$A$2:$E$16,Tasks!F295,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F295" s="6">
         <v>2</v>
@@ -7957,11 +7961,11 @@
         <v>31</v>
       </c>
       <c r="D299">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E299" s="5">
         <f>VLOOKUP(B299,Assignee!$A$2:$E$16,Tasks!F299,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F299" s="6">
         <v>3</v>
@@ -8029,11 +8033,11 @@
         <v>25</v>
       </c>
       <c r="D302">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E302" s="5">
         <f>VLOOKUP(B302,Assignee!$A$2:$E$16,Tasks!F302,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F302" s="6">
         <v>2</v>
@@ -8341,11 +8345,11 @@
         <v>25</v>
       </c>
       <c r="D315">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E315" s="5">
         <f>VLOOKUP(B315,Assignee!$A$2:$E$16,Tasks!F315,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F315" s="6">
         <v>2</v>
@@ -8509,11 +8513,11 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E322" s="5">
         <f>VLOOKUP(B322,Assignee!$A$2:$E$16,Tasks!F322,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F322" s="6">
         <v>4</v>
@@ -8653,11 +8657,11 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E328" s="5">
         <f>VLOOKUP(B328,Assignee!$A$2:$E$16,Tasks!F328,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F328" s="6">
         <v>4</v>
@@ -8797,11 +8801,11 @@
         <v>25</v>
       </c>
       <c r="D334">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E334" s="5">
         <f>VLOOKUP(B334,Assignee!$A$2:$E$16,Tasks!F334,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F334" s="6">
         <v>2</v>
@@ -8917,11 +8921,11 @@
         <v>25</v>
       </c>
       <c r="D339">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E339" s="5">
         <f>VLOOKUP(B339,Assignee!$A$2:$E$16,Tasks!F339,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F339" s="6">
         <v>2</v>
@@ -9301,11 +9305,11 @@
         <v>25</v>
       </c>
       <c r="D355">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E355" s="5">
         <f>VLOOKUP(B355,Assignee!$A$2:$E$16,Tasks!F355,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F355" s="6">
         <v>2</v>
@@ -9349,11 +9353,11 @@
         <v>25</v>
       </c>
       <c r="D357">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E357" s="5">
         <f>VLOOKUP(B357,Assignee!$A$2:$E$16,Tasks!F357,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F357" s="6">
         <v>2</v>
@@ -9541,11 +9545,11 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E365" s="5">
         <f>VLOOKUP(B365,Assignee!$A$2:$E$16,Tasks!F365,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F365" s="6">
         <v>4</v>
@@ -9829,11 +9833,11 @@
         <v>25</v>
       </c>
       <c r="D377">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E377" s="5">
         <f>VLOOKUP(B377,Assignee!$A$2:$E$16,Tasks!F377,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F377" s="6">
         <v>2</v>
@@ -10189,11 +10193,11 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E392" s="5">
         <f>VLOOKUP(B392,Assignee!$A$2:$E$16,Tasks!F392,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F392" s="6">
         <v>4</v>
@@ -10213,11 +10217,11 @@
         <v>25</v>
       </c>
       <c r="D393">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E393" s="5">
         <f>VLOOKUP(B393,Assignee!$A$2:$E$16,Tasks!F393,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F393" s="6">
         <v>2</v>
@@ -10477,11 +10481,11 @@
         <v>25</v>
       </c>
       <c r="D404">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E404" s="5">
         <f>VLOOKUP(B404,Assignee!$A$2:$E$16,Tasks!F404,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F404" s="6">
         <v>2</v>
@@ -10525,11 +10529,11 @@
         <v>25</v>
       </c>
       <c r="D406">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E406" s="5">
         <f>VLOOKUP(B406,Assignee!$A$2:$E$16,Tasks!F406,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F406" s="6">
         <v>2</v>
@@ -10597,11 +10601,11 @@
         <v>31</v>
       </c>
       <c r="D409">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E409" s="5">
         <f>VLOOKUP(B409,Assignee!$A$2:$E$16,Tasks!F409,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F409" s="6">
         <v>3</v>
@@ -10789,11 +10793,11 @@
         <v>25</v>
       </c>
       <c r="D417">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E417" s="5">
         <f>VLOOKUP(B417,Assignee!$A$2:$E$16,Tasks!F417,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F417" s="6">
         <v>2</v>
@@ -10813,11 +10817,11 @@
         <v>25</v>
       </c>
       <c r="D418">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E418" s="5">
         <f>VLOOKUP(B418,Assignee!$A$2:$E$16,Tasks!F418,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F418" s="6">
         <v>2</v>
@@ -10933,11 +10937,11 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E423" s="5">
         <f>VLOOKUP(B423,Assignee!$A$2:$E$16,Tasks!F423,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F423" s="6">
         <v>4</v>
@@ -11077,11 +11081,11 @@
         <v>25</v>
       </c>
       <c r="D429">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E429" s="5">
         <f>VLOOKUP(B429,Assignee!$A$2:$E$16,Tasks!F429,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F429" s="6">
         <v>2</v>
@@ -11101,11 +11105,11 @@
         <v>31</v>
       </c>
       <c r="D430">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E430" s="5">
         <f>VLOOKUP(B430,Assignee!$A$2:$E$16,Tasks!F430,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F430" s="6">
         <v>3</v>
@@ -11245,11 +11249,11 @@
         <v>25</v>
       </c>
       <c r="D436">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E436" s="5">
         <f>VLOOKUP(B436,Assignee!$A$2:$E$16,Tasks!F436,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F436" s="6">
         <v>2</v>
@@ -11581,11 +11585,11 @@
         <v>31</v>
       </c>
       <c r="D450">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E450" s="5">
         <f>VLOOKUP(B450,Assignee!$A$2:$E$16,Tasks!F450,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F450" s="6">
         <v>3</v>
@@ -11677,11 +11681,11 @@
         <v>25</v>
       </c>
       <c r="D454">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E454" s="5">
         <f>VLOOKUP(B454,Assignee!$A$2:$E$16,Tasks!F454,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F454" s="6">
         <v>2</v>
@@ -11965,11 +11969,11 @@
         <v>31</v>
       </c>
       <c r="D466">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E466" s="5">
         <f>VLOOKUP(B466,Assignee!$A$2:$E$16,Tasks!F466,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F466" s="6">
         <v>3</v>
@@ -12133,11 +12137,11 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E473" s="5">
         <f>VLOOKUP(B473,Assignee!$A$2:$E$16,Tasks!F473,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F473" s="6">
         <v>4</v>
@@ -12469,11 +12473,11 @@
         <v>25</v>
       </c>
       <c r="D487">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E487" s="5">
         <f>VLOOKUP(B487,Assignee!$A$2:$E$16,Tasks!F487,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F487" s="6">
         <v>2</v>
@@ -12637,11 +12641,11 @@
         <v>25</v>
       </c>
       <c r="D494">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E494" s="5">
         <f>VLOOKUP(B494,Assignee!$A$2:$E$16,Tasks!F494,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F494" s="6">
         <v>2</v>
@@ -12685,11 +12689,11 @@
         <v>25</v>
       </c>
       <c r="D496">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E496" s="5">
         <f>VLOOKUP(B496,Assignee!$A$2:$E$16,Tasks!F496,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F496" s="6">
         <v>2</v>
@@ -12709,11 +12713,11 @@
         <v>31</v>
       </c>
       <c r="D497">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E497" s="5">
         <f>VLOOKUP(B497,Assignee!$A$2:$E$16,Tasks!F497,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F497" s="6">
         <v>3</v>
@@ -12733,11 +12737,11 @@
         <v>31</v>
       </c>
       <c r="D498">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E498" s="5">
         <f>VLOOKUP(B498,Assignee!$A$2:$E$16,Tasks!F498,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F498" s="6">
         <v>3</v>
@@ -12757,11 +12761,11 @@
         <v>25</v>
       </c>
       <c r="D499">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E499" s="5">
         <f>VLOOKUP(B499,Assignee!$A$2:$E$16,Tasks!F499,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F499" s="6">
         <v>2</v>
@@ -12829,11 +12833,11 @@
         <v>25</v>
       </c>
       <c r="D502">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E502" s="5">
         <f>VLOOKUP(B502,Assignee!$A$2:$E$16,Tasks!F502,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F502" s="6">
         <v>2</v>
@@ -12901,11 +12905,11 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E505" s="5">
         <f>VLOOKUP(B505,Assignee!$A$2:$E$16,Tasks!F505,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F505" s="6">
         <v>4</v>
@@ -12997,11 +13001,11 @@
         <v>25</v>
       </c>
       <c r="D509">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E509" s="5">
         <f>VLOOKUP(B509,Assignee!$A$2:$E$16,Tasks!F509,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F509" s="6">
         <v>2</v>
@@ -13021,11 +13025,11 @@
         <v>25</v>
       </c>
       <c r="D510">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E510" s="5">
         <f>VLOOKUP(B510,Assignee!$A$2:$E$16,Tasks!F510,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F510" s="6">
         <v>2</v>
@@ -13189,11 +13193,11 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E517" s="5">
         <f>VLOOKUP(B517,Assignee!$A$2:$E$16,Tasks!F517,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F517" s="6">
         <v>4</v>
@@ -13213,11 +13217,11 @@
         <v>25</v>
       </c>
       <c r="D518">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E518" s="5">
         <f>VLOOKUP(B518,Assignee!$A$2:$E$16,Tasks!F518,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F518" s="6">
         <v>2</v>
@@ -13405,11 +13409,11 @@
         <v>25</v>
       </c>
       <c r="D526">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E526" s="5">
         <f>VLOOKUP(B526,Assignee!$A$2:$E$16,Tasks!F526,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F526" s="6">
         <v>2</v>
@@ -13453,11 +13457,11 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E528" s="5">
         <f>VLOOKUP(B528,Assignee!$A$2:$E$16,Tasks!F528,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F528" s="6">
         <v>4</v>
@@ -13597,11 +13601,11 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E534" s="5">
         <f>VLOOKUP(B534,Assignee!$A$2:$E$16,Tasks!F534,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F534" s="6">
         <v>4</v>
@@ -13885,11 +13889,11 @@
         <v>25</v>
       </c>
       <c r="D546">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E546" s="5">
         <f>VLOOKUP(B546,Assignee!$A$2:$E$16,Tasks!F546,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F546" s="6">
         <v>2</v>
@@ -14029,11 +14033,11 @@
         <v>25</v>
       </c>
       <c r="D552">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E552" s="5">
         <f>VLOOKUP(B552,Assignee!$A$2:$E$16,Tasks!F552,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F552" s="6">
         <v>2</v>
@@ -14317,11 +14321,11 @@
         <v>31</v>
       </c>
       <c r="D564">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E564" s="5">
         <f>VLOOKUP(B564,Assignee!$A$2:$E$16,Tasks!F564,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F564" s="6">
         <v>3</v>
@@ -14461,11 +14465,11 @@
         <v>25</v>
       </c>
       <c r="D570">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E570" s="5">
         <f>VLOOKUP(B570,Assignee!$A$2:$E$16,Tasks!F570,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F570" s="6">
         <v>2</v>
@@ -14677,11 +14681,11 @@
         <v>25</v>
       </c>
       <c r="D579">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E579" s="5">
         <f>VLOOKUP(B579,Assignee!$A$2:$E$16,Tasks!F579,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F579" s="6">
         <v>2</v>
@@ -15109,11 +15113,11 @@
         <v>25</v>
       </c>
       <c r="D597">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E597" s="5">
         <f>VLOOKUP(B597,Assignee!$A$2:$E$16,Tasks!F597,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F597" s="6">
         <v>2</v>
@@ -15277,11 +15281,11 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E604" s="5">
         <f>VLOOKUP(B604,Assignee!$A$2:$E$16,Tasks!F604,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F604" s="6">
         <v>4</v>
@@ -15373,11 +15377,11 @@
         <v>25</v>
       </c>
       <c r="D608">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E608" s="5">
         <f>VLOOKUP(B608,Assignee!$A$2:$E$16,Tasks!F608,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F608" s="6">
         <v>2</v>
@@ -15421,11 +15425,11 @@
         <v>25</v>
       </c>
       <c r="D610">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E610" s="5">
         <f>VLOOKUP(B610,Assignee!$A$2:$E$16,Tasks!F610,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F610" s="6">
         <v>2</v>
@@ -15565,11 +15569,11 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E616" s="5">
         <f>VLOOKUP(B616,Assignee!$A$2:$E$16,Tasks!F616,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F616" s="6">
         <v>4</v>
@@ -15637,11 +15641,11 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E619" s="5">
         <f>VLOOKUP(B619,Assignee!$A$2:$E$16,Tasks!F619,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F619" s="6">
         <v>4</v>
@@ -15757,11 +15761,11 @@
         <v>25</v>
       </c>
       <c r="D624">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E624" s="5">
         <f>VLOOKUP(B624,Assignee!$A$2:$E$16,Tasks!F624,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F624" s="6">
         <v>2</v>
@@ -15949,11 +15953,11 @@
         <v>25</v>
       </c>
       <c r="D632">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E632" s="5">
         <f>VLOOKUP(B632,Assignee!$A$2:$E$16,Tasks!F632,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F632" s="6">
         <v>2</v>
@@ -15973,11 +15977,11 @@
         <v>25</v>
       </c>
       <c r="D633">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E633" s="5">
         <f>VLOOKUP(B633,Assignee!$A$2:$E$16,Tasks!F633,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F633" s="6">
         <v>2</v>
@@ -16021,11 +16025,11 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E635" s="5">
         <f>VLOOKUP(B635,Assignee!$A$2:$E$16,Tasks!F635,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F635" s="6">
         <v>4</v>
@@ -16069,11 +16073,11 @@
         <v>31</v>
       </c>
       <c r="D637">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E637" s="5">
         <f>VLOOKUP(B637,Assignee!$A$2:$E$16,Tasks!F637,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F637" s="6">
         <v>3</v>
@@ -16141,11 +16145,11 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E640" s="5">
         <f>VLOOKUP(B640,Assignee!$A$2:$E$16,Tasks!F640,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F640" s="6">
         <v>4</v>
@@ -16357,11 +16361,11 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E649" s="5">
         <f>VLOOKUP(B649,Assignee!$A$2:$E$16,Tasks!F649,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F649" s="6">
         <v>4</v>
@@ -16453,11 +16457,11 @@
         <v>25</v>
       </c>
       <c r="D653">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E653" s="5">
         <f>VLOOKUP(B653,Assignee!$A$2:$E$16,Tasks!F653,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F653" s="6">
         <v>2</v>
@@ -16573,11 +16577,11 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E658" s="5">
         <f>VLOOKUP(B658,Assignee!$A$2:$E$16,Tasks!F658,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F658" s="6">
         <v>4</v>
@@ -16669,11 +16673,11 @@
         <v>25</v>
       </c>
       <c r="D662">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E662" s="5">
         <f>VLOOKUP(B662,Assignee!$A$2:$E$16,Tasks!F662,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F662" s="6">
         <v>2</v>
@@ -16717,11 +16721,11 @@
         <v>25</v>
       </c>
       <c r="D664">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E664" s="5">
         <f>VLOOKUP(B664,Assignee!$A$2:$E$16,Tasks!F664,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F664" s="6">
         <v>2</v>
@@ -16765,11 +16769,11 @@
         <v>25</v>
       </c>
       <c r="D666">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E666" s="5">
         <f>VLOOKUP(B666,Assignee!$A$2:$E$16,Tasks!F666,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F666" s="6">
         <v>2</v>
@@ -16861,11 +16865,11 @@
         <v>25</v>
       </c>
       <c r="D670">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E670" s="5">
         <f>VLOOKUP(B670,Assignee!$A$2:$E$16,Tasks!F670,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F670" s="6">
         <v>2</v>
@@ -16933,11 +16937,11 @@
         <v>25</v>
       </c>
       <c r="D673">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E673" s="5">
         <f>VLOOKUP(B673,Assignee!$A$2:$E$16,Tasks!F673,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F673" s="6">
         <v>2</v>
@@ -16957,11 +16961,11 @@
         <v>25</v>
       </c>
       <c r="D674">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E674" s="5">
         <f>VLOOKUP(B674,Assignee!$A$2:$E$16,Tasks!F674,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F674" s="6">
         <v>2</v>
@@ -17485,11 +17489,11 @@
         <v>25</v>
       </c>
       <c r="D696">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E696" s="5">
         <f>VLOOKUP(B696,Assignee!$A$2:$E$16,Tasks!F696,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F696" s="6">
         <v>2</v>
@@ -17629,11 +17633,11 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E702" s="5">
         <f>VLOOKUP(B702,Assignee!$A$2:$E$16,Tasks!F702,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F702" s="6">
         <v>4</v>
@@ -18037,11 +18041,11 @@
         <v>31</v>
       </c>
       <c r="D719">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E719" s="5">
         <f>VLOOKUP(B719,Assignee!$A$2:$E$16,Tasks!F719,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F719" s="6">
         <v>3</v>
@@ -18373,11 +18377,11 @@
         <v>25</v>
       </c>
       <c r="D733">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E733" s="5">
         <f>VLOOKUP(B733,Assignee!$A$2:$E$16,Tasks!F733,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F733" s="6">
         <v>2</v>
@@ -18877,11 +18881,11 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E754" s="5">
         <f>VLOOKUP(B754,Assignee!$A$2:$E$16,Tasks!F754,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F754" s="6">
         <v>4</v>
@@ -19741,11 +19745,11 @@
         <v>25</v>
       </c>
       <c r="D790">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E790" s="5">
         <f>VLOOKUP(B790,Assignee!$A$2:$E$16,Tasks!F790,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F790" s="6">
         <v>2</v>
@@ -19813,11 +19817,11 @@
         <v>25</v>
       </c>
       <c r="D793">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E793" s="5">
         <f>VLOOKUP(B793,Assignee!$A$2:$E$16,Tasks!F793,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F793" s="6">
         <v>2</v>
@@ -19981,11 +19985,11 @@
         <v>31</v>
       </c>
       <c r="D800">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E800" s="5">
         <f>VLOOKUP(B800,Assignee!$A$2:$E$16,Tasks!F800,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F800" s="6">
         <v>3</v>
@@ -20005,11 +20009,11 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E801" s="5">
         <f>VLOOKUP(B801,Assignee!$A$2:$E$16,Tasks!F801,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F801" s="6">
         <v>4</v>
@@ -20317,11 +20321,11 @@
         <v>25</v>
       </c>
       <c r="D814">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E814" s="5">
         <f>VLOOKUP(B814,Assignee!$A$2:$E$16,Tasks!F814,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F814" s="6">
         <v>2</v>
@@ -20389,11 +20393,11 @@
         <v>31</v>
       </c>
       <c r="D817">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E817" s="5">
         <f>VLOOKUP(B817,Assignee!$A$2:$E$16,Tasks!F817,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F817" s="6">
         <v>3</v>
@@ -20413,11 +20417,11 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>16.32</v>
+        <v>15.120000000000001</v>
       </c>
       <c r="E818" s="5">
         <f>VLOOKUP(B818,Assignee!$A$2:$E$16,Tasks!F818,0)</f>
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F818" s="6">
         <v>4</v>
@@ -20725,11 +20729,11 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E831" s="5">
         <f>VLOOKUP(B831,Assignee!$A$2:$E$16,Tasks!F831,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F831" s="6">
         <v>4</v>
@@ -20797,11 +20801,11 @@
         <v>25</v>
       </c>
       <c r="D834">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E834" s="5">
         <f>VLOOKUP(B834,Assignee!$A$2:$E$16,Tasks!F834,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F834" s="6">
         <v>2</v>
@@ -20941,11 +20945,11 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E840" s="5">
         <f>VLOOKUP(B840,Assignee!$A$2:$E$16,Tasks!F840,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F840" s="6">
         <v>4</v>
@@ -20989,11 +20993,11 @@
         <v>31</v>
       </c>
       <c r="D842">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E842" s="5">
         <f>VLOOKUP(B842,Assignee!$A$2:$E$16,Tasks!F842,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F842" s="6">
         <v>3</v>
@@ -21109,11 +21113,11 @@
         <v>31</v>
       </c>
       <c r="D847">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E847" s="5">
         <f>VLOOKUP(B847,Assignee!$A$2:$E$16,Tasks!F847,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F847" s="6">
         <v>3</v>
@@ -21205,11 +21209,11 @@
         <v>25</v>
       </c>
       <c r="D851">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E851" s="5">
         <f>VLOOKUP(B851,Assignee!$A$2:$E$16,Tasks!F851,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F851" s="6">
         <v>2</v>
@@ -21541,11 +21545,11 @@
         <v>25</v>
       </c>
       <c r="D865">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E865" s="5">
         <f>VLOOKUP(B865,Assignee!$A$2:$E$16,Tasks!F865,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F865" s="6">
         <v>2</v>
@@ -21733,11 +21737,11 @@
         <v>25</v>
       </c>
       <c r="D873">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E873" s="5">
         <f>VLOOKUP(B873,Assignee!$A$2:$E$16,Tasks!F873,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F873" s="6">
         <v>2</v>
@@ -21877,11 +21881,11 @@
         <v>31</v>
       </c>
       <c r="D879">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E879" s="5">
         <f>VLOOKUP(B879,Assignee!$A$2:$E$16,Tasks!F879,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F879" s="6">
         <v>3</v>
@@ -22093,11 +22097,11 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E888" s="5">
         <f>VLOOKUP(B888,Assignee!$A$2:$E$16,Tasks!F888,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F888" s="6">
         <v>4</v>
@@ -22837,11 +22841,11 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E919" s="5">
         <f>VLOOKUP(B919,Assignee!$A$2:$E$16,Tasks!F919,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F919" s="6">
         <v>4</v>
@@ -22933,11 +22937,11 @@
         <v>31</v>
       </c>
       <c r="D923">
-        <v>11.2</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="E923" s="5">
         <f>VLOOKUP(B923,Assignee!$A$2:$E$16,Tasks!F923,0)</f>
-        <v>1.4</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F923" s="6">
         <v>3</v>
@@ -23005,11 +23009,11 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E926" s="5">
         <f>VLOOKUP(B926,Assignee!$A$2:$E$16,Tasks!F926,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F926" s="6">
         <v>4</v>
@@ -23077,11 +23081,11 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>16.080000000000002</v>
+        <v>15.36</v>
       </c>
       <c r="E929" s="5">
         <f>VLOOKUP(B929,Assignee!$A$2:$E$16,Tasks!F929,0)</f>
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="F929" s="6">
         <v>4</v>
@@ -23245,11 +23249,11 @@
         <v>25</v>
       </c>
       <c r="D936">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E936" s="5">
         <f>VLOOKUP(B936,Assignee!$A$2:$E$16,Tasks!F936,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F936" s="6">
         <v>2</v>
@@ -23317,11 +23321,11 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E939" s="5">
         <f>VLOOKUP(B939,Assignee!$A$2:$E$16,Tasks!F939,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F939" s="6">
         <v>4</v>
@@ -23605,11 +23609,11 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>8.64</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="E951" s="5">
         <f>VLOOKUP(B951,Assignee!$A$2:$E$16,Tasks!F951,0)</f>
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="F951" s="6">
         <v>4</v>
@@ -23773,11 +23777,11 @@
         <v>25</v>
       </c>
       <c r="D958">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E958" s="5">
         <f>VLOOKUP(B958,Assignee!$A$2:$E$16,Tasks!F958,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F958" s="6">
         <v>2</v>
@@ -23797,11 +23801,11 @@
         <v>25</v>
       </c>
       <c r="D959">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E959" s="5">
         <f>VLOOKUP(B959,Assignee!$A$2:$E$16,Tasks!F959,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F959" s="6">
         <v>2</v>
@@ -23893,11 +23897,11 @@
         <v>25</v>
       </c>
       <c r="D963">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E963" s="5">
         <f>VLOOKUP(B963,Assignee!$A$2:$E$16,Tasks!F963,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F963" s="6">
         <v>2</v>
@@ -24253,11 +24257,11 @@
         <v>25</v>
       </c>
       <c r="D978">
-        <v>6.6000000000000005</v>
+        <v>5.3500000000000005</v>
       </c>
       <c r="E978" s="5">
         <f>VLOOKUP(B978,Assignee!$A$2:$E$16,Tasks!F978,0)</f>
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F978" s="6">
         <v>2</v>
@@ -24349,11 +24353,11 @@
         <v>25</v>
       </c>
       <c r="D982">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="E982" s="5">
         <f>VLOOKUP(B982,Assignee!$A$2:$E$16,Tasks!F982,0)</f>
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="F982" s="6">
         <v>2</v>
@@ -24373,11 +24377,11 @@
         <v>25</v>
       </c>
       <c r="D983">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E983" s="5">
         <f>VLOOKUP(B983,Assignee!$A$2:$E$16,Tasks!F983,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F983" s="6">
         <v>2</v>
@@ -24589,11 +24593,11 @@
         <v>25</v>
       </c>
       <c r="D992">
-        <v>6.65</v>
+        <v>6.45</v>
       </c>
       <c r="E992" s="5">
         <f>VLOOKUP(B992,Assignee!$A$2:$E$16,Tasks!F992,0)</f>
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F992" s="6">
         <v>2</v>
@@ -24637,11 +24641,11 @@
         <v>25</v>
       </c>
       <c r="D994">
-        <v>6.5500000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E994" s="5">
         <f>VLOOKUP(B994,Assignee!$A$2:$E$16,Tasks!F994,0)</f>
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F994" s="6">
         <v>2</v>
@@ -24781,11 +24785,11 @@
         <v>31</v>
       </c>
       <c r="D1000">
-        <v>11.44</v>
+        <v>9.84</v>
       </c>
       <c r="E1000" s="5">
         <f>VLOOKUP(B1000,Assignee!$A$2:$E$16,Tasks!F1000,0)</f>
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="F1000" s="6">
         <v>3</v>
@@ -24819,6 +24823,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1001" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
